--- a/時光嶼_櫃檯服務備忘錄.xlsx
+++ b/時光嶼_櫃檯服務備忘錄.xlsx
@@ -11,7 +11,7 @@
     <sheet name="使用說明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'時光嶼'!$A$2:$J$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'時光嶼'!$A$2:$J$133</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -583,11 +583,11 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>14A3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -601,12 +601,18 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>70</v>
+      </c>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>同 14A3 屋主</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -615,30 +621,38 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>14A5</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>陳玟沂</t>
+          <t>毛若蘭 / 副主任委員-李英華</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>0988-330980 / 0926-241019(夫)</t>
+          <t>0913-326051</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>6</v>
+      </c>
       <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>副主任委員</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -647,36 +661,36 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>黃國禎(租建材行) 租：余先生(承強)</t>
+          <t>蔡侑岑</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>0985-077777(余R) / 0900-615707(郭S)</t>
+          <t>0910-678283 / 0972-928891(夫)</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>17</v>
+        <v>128</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>建材行租戶</t>
-        </is>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -685,34 +699,30 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>3A1</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>歐陽子元(租建材行)</t>
+          <t>林聖雄</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>0985-077777(余R)</t>
+          <t>0982-599021 / 0979-255582(妻)</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="G6" s="6" t="inlineStr"/>
       <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>建材行租戶</t>
-        </is>
-      </c>
+      <c r="J6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -721,27 +731,29 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2B2</t>
+          <t>3A2</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>陳嘉彬</t>
+          <t>丁偉晃</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>0-</t>
+          <t>0910-118175(父)</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>148</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
+        <v>108</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>109</v>
+      </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr"/>
@@ -753,27 +765,29 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>2B3</t>
+          <t>3A3</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>蔡亞臻</t>
+          <t>白怡蕖</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>0931-474150 / 04-24738819</t>
+          <t>0911-662504 / 0926-665766(林R)</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="G8" s="6" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>47</v>
+      </c>
       <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" s="6" t="inlineStr"/>
       <c r="J8" s="7" t="inlineStr"/>
@@ -785,34 +799,32 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2B7</t>
+          <t>3A5</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>施碧虹</t>
+          <t>劉敏宏</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>0- 同S6</t>
+          <t>0-</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>147</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>67</v>
+      </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>電話同S6</t>
-        </is>
-      </c>
+      <c r="J9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -821,30 +833,36 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>3B1</t>
+          <t>4A1</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>甘慧之</t>
+          <t>事務委員-沈士艷</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>0988-861001</t>
+          <t>0927-377222</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>63</v>
+      </c>
       <c r="H10" s="6" t="inlineStr"/>
       <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="7" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>事務委員</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -853,25 +871,25 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>3B2</t>
+          <t>4A2</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>楊政達</t>
+          <t>許惟舜</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>0936-760105 / 0909-132606</t>
+          <t>0985-928006 / 0916-760883(妻)</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr"/>
@@ -885,27 +903,29 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>3B3</t>
+          <t>4A3</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>郭慕慈</t>
+          <t>鐘予彣</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>0-</t>
+          <t>0976-099952 / 0982-728281(夫)</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr"/>
+        <v>126</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>127</v>
+      </c>
       <c r="H12" s="6" t="inlineStr"/>
       <c r="I12" s="6" t="inlineStr"/>
       <c r="J12" s="7" t="inlineStr"/>
@@ -917,27 +937,29 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>3+4B5</t>
+          <t>4A5</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>邱若瑜</t>
+          <t>洪劓翔</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>0952-695232 / 0922-709299(夫)</t>
+          <t>0917-818478 / 0972-906739(妻)</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
+        <v>103</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>107</v>
+      </c>
       <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="4" t="inlineStr"/>
@@ -949,25 +971,25 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>3+4B6</t>
+          <t>5A1</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>黃姿綺</t>
+          <t>張庭偉</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>0912-758400</t>
+          <t>0-</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>58</v>
+        <v>149</v>
       </c>
       <c r="G14" s="6" t="inlineStr"/>
       <c r="H14" s="6" t="inlineStr"/>
@@ -981,27 +1003,29 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>3B7</t>
+          <t>5A2</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>周韋辰</t>
+          <t>李一民</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>0987-797088 / 0937-252032</t>
+          <t>0-</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>55</v>
+      </c>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="4" t="inlineStr"/>
@@ -1013,16 +1037,16 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>3B8</t>
+          <t>5A3</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>盧宣名</t>
+          <t>楊美滿</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -1031,7 +1055,7 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>8</v>
+        <v>115</v>
       </c>
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="6" t="inlineStr"/>
@@ -1045,25 +1069,25 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>4B1</t>
+          <t>5A5</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>黃軒奕</t>
+          <t>譚言家</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>0936-709718 / 0985-441557(同住)</t>
+          <t>0988-720465 / 0923-864231(夫)</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr"/>
@@ -1077,25 +1101,25 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>4B2</t>
+          <t>6A1</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>廖英如</t>
+          <t>陳沛琪</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>0978-717518 / 04-24758092</t>
+          <t>0919-436641</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="G18" s="6" t="inlineStr"/>
       <c r="H18" s="6" t="inlineStr"/>
@@ -1109,29 +1133,27 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>4B3</t>
+          <t>6A2</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>潘芳儀</t>
+          <t>劉嘉侖</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>0975-781832 / 0970-520929(夫)</t>
+          <t>0911-087503</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>34</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="4" t="inlineStr"/>
@@ -1143,25 +1165,25 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>4B7</t>
+          <t>6A3</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>陳麗如</t>
+          <t>仕宗旻</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>0-</t>
+          <t>0923-630140</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="6" t="inlineStr"/>
@@ -1175,25 +1197,25 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>4B8</t>
+          <t>6A5</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>黃美華</t>
+          <t>李柏諭</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>0975-043914 / 0935-602038</t>
+          <t>0-</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>29</v>
+        <v>116</v>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr"/>
@@ -1207,30 +1229,34 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5B1</t>
+          <t>7A1</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>張雅雯</t>
+          <t>主任委員-羅仁智 / 租-許小姐</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>0923-355242 / 0988-755886(夫)</t>
+          <t>0933-337593 / 租 0931-930300</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>15</v>
+        <v>167</v>
       </c>
       <c r="G22" s="6" t="inlineStr"/>
       <c r="H22" s="6" t="inlineStr"/>
       <c r="I22" s="6" t="inlineStr"/>
-      <c r="J22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>主任委員；出租中</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1239,25 +1265,25 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>5B2</t>
+          <t>7A2</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>朱明珍</t>
+          <t>楊淮鈞</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>0953-928558</t>
+          <t>0-</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="inlineStr"/>
@@ -1271,25 +1297,25 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>5B3</t>
+          <t>7A3</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>張朝銘</t>
+          <t>李佳蓉</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>0953-775513 / 0921-498553</t>
+          <t>0975-785715 / 0988-289174(夫)</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="G24" s="6" t="inlineStr"/>
       <c r="H24" s="6" t="inlineStr"/>
@@ -1303,27 +1329,29 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>5+6B5</t>
+          <t>7A5</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>謝雨潤</t>
+          <t>鄭家琪</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>0980-152552 / 0928-261809(妻)</t>
+          <t>0910-996882 / 0937-842175(夫)</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="G25" s="3" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>45</v>
+      </c>
       <c r="H25" s="3" t="inlineStr"/>
       <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="4" t="inlineStr"/>
@@ -1335,27 +1363,29 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>5+6B6</t>
+          <t>8A1</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>林桂玉</t>
+          <t>蔡宜臻</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>0-</t>
+          <t>0910-372132 / 0973-085866(父)</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="G26" s="6" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>125</v>
+      </c>
       <c r="H26" s="6" t="inlineStr"/>
       <c r="I26" s="6" t="inlineStr"/>
       <c r="J26" s="7" t="inlineStr"/>
@@ -1367,25 +1397,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>5B7</t>
+          <t>8A2</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>高袖華</t>
+          <t>廖玲君</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>0986-635786 / 0937-285830(夫)</t>
+          <t>0910-608736 / 0972-385833(夫)</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="3" t="inlineStr"/>
@@ -1399,25 +1429,25 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>5B8</t>
+          <t>8A3</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>賴雅惠</t>
+          <t>廖美宜</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>0936-960900</t>
+          <t>0931-422931 / 0937-596379(莊R)</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="G28" s="6" t="inlineStr"/>
       <c r="H28" s="6" t="inlineStr"/>
@@ -1431,16 +1461,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>6B1</t>
+          <t>8A5</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>林桂鳳</t>
+          <t>雨浩股份有限公司</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1449,12 +1479,16 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>30</v>
+        <v>118</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="3" t="inlineStr"/>
       <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="4" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>法人戶</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -1463,25 +1497,25 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>6B2</t>
+          <t>9A1</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>晉安</t>
+          <t>莊宜正</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>0919-035076 / 0931-720858(同住) / 0912-750260</t>
+          <t>0937-596379</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="G30" s="6" t="inlineStr"/>
       <c r="H30" s="6" t="inlineStr"/>
@@ -1495,27 +1529,29 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>6B3</t>
+          <t>9A2</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>張修毓</t>
+          <t>蔡宜娟</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>0921-628527(妻)</t>
+          <t>0921-752975 / 0928-669686(夫)</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>97</v>
-      </c>
-      <c r="G31" s="3" t="inlineStr"/>
+        <v>112</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>137</v>
+      </c>
       <c r="H31" s="3" t="inlineStr"/>
       <c r="I31" s="3" t="inlineStr"/>
       <c r="J31" s="4" t="inlineStr"/>
@@ -1527,25 +1563,25 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>6B7</t>
+          <t>9A3</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>鄭永發</t>
+          <t>陳語婷</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>0980-607784 / 0919-810888(妻)</t>
+          <t>0988-516150</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="G32" s="6" t="inlineStr"/>
       <c r="H32" s="6" t="inlineStr"/>
@@ -1559,32 +1595,34 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>6B8</t>
+          <t>9A5</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>財務委員-洪冠華</t>
+          <t>租-陳泓諾</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>0925-270614 / 0937-299595(父)</t>
+          <t>0924-163822 / 0971-491319</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G33" s="3" t="inlineStr"/>
+        <v>113</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>114</v>
+      </c>
       <c r="H33" s="3" t="inlineStr"/>
       <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>財務委員</t>
+          <t>出租中</t>
         </is>
       </c>
     </row>
@@ -1595,25 +1633,25 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>7B1</t>
+          <t>10A1</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>張軒鴻</t>
+          <t>蔡沅辰</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>0977-236156</t>
+          <t>0989-182727</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="G34" s="6" t="inlineStr"/>
       <c r="H34" s="6" t="inlineStr"/>
@@ -1627,27 +1665,29 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>7B2</t>
+          <t>10A2</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>洪翊峰</t>
+          <t>王藝庭</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>0919-745641 / 0932-677334(父)</t>
+          <t>0912-704344 / 0933-336245(夫)</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G35" s="3" t="inlineStr"/>
+        <v>105</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>106</v>
+      </c>
       <c r="H35" s="3" t="inlineStr"/>
       <c r="I35" s="3" t="inlineStr"/>
       <c r="J35" s="4" t="inlineStr"/>
@@ -1659,32 +1699,30 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>7B3</t>
+          <t>10A3</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>吳弘信</t>
+          <t>吳浩廷</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>0976-038366</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr"/>
+          <t>0-</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>101</v>
+      </c>
       <c r="G36" s="6" t="inlineStr"/>
       <c r="H36" s="6" t="inlineStr"/>
       <c r="I36" s="6" t="inlineStr"/>
-      <c r="J36" s="7" t="inlineStr">
-        <is>
-          <t>車位資料請複核</t>
-        </is>
-      </c>
+      <c r="J36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1693,25 +1731,25 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>7+8B5</t>
+          <t>10A5</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>楊嘉凱</t>
+          <t>李綉玲</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>0989-748555(妻) / 0963-204310</t>
+          <t>0955-524689 / 0936-497699(夫)</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
       <c r="H37" s="3" t="inlineStr"/>
@@ -1725,25 +1763,25 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>7+8B6</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>詹偉哲</t>
+          <t>蔡曜興</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>0932-247258(父)</t>
+          <t>0-</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>156</v>
+        <v>102</v>
       </c>
       <c r="G38" s="6" t="inlineStr"/>
       <c r="H38" s="6" t="inlineStr"/>
@@ -1757,27 +1795,29 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>7B7</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>吳振宇</t>
+          <t>吳宜珊</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>0-</t>
+          <t>0972-077013 / 0972-313724(弟)</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>153</v>
-      </c>
-      <c r="G39" s="3" t="inlineStr"/>
+        <v>123</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>124</v>
+      </c>
       <c r="H39" s="3" t="inlineStr"/>
       <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="4" t="inlineStr"/>
@@ -1789,27 +1829,29 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>7B8</t>
+          <t>11A3</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>譚文政</t>
+          <t>劉庭瑋</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>0966-770876 / 0987-372895(妻)</t>
+          <t>0918-118179 / 0920-118179(父)</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="G40" s="6" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>92</v>
+      </c>
       <c r="H40" s="6" t="inlineStr"/>
       <c r="I40" s="6" t="inlineStr"/>
       <c r="J40" s="7" t="inlineStr"/>
@@ -1821,25 +1863,25 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>8B1</t>
+          <t>11A5</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>蘇欽洲</t>
+          <t>李奕憲</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>0919-631434 / 0937-781353(賴士超)</t>
+          <t>0-</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="G41" s="3" t="inlineStr"/>
       <c r="H41" s="3" t="inlineStr"/>
@@ -1853,25 +1895,25 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>8B2</t>
+          <t>12A1</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>曾昱泰</t>
+          <t>謝絜如</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>0988-173077</t>
+          <t>0909-663563 / 0909-872672(夫)</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="G42" s="6" t="inlineStr"/>
       <c r="H42" s="6" t="inlineStr"/>
@@ -1885,27 +1927,29 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>8B3</t>
+          <t>12A2</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>黃礦衛</t>
+          <t>許靜宜</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>0934-072601 / 0930-671667(妻)</t>
+          <t>0921-398859 / 0915-510100(夫)</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>138</v>
-      </c>
-      <c r="G43" s="3" t="inlineStr"/>
+        <v>163</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>164</v>
+      </c>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="4" t="inlineStr"/>
@@ -1917,36 +1961,30 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>8B7</t>
+          <t>12A3</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>前屋主：簡宗哲 / 新屋主：呂紹榮</t>
+          <t>李杰陽</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>0938-869298 / 0975-029305(妻)</t>
+          <t>0912-407710 / 0966-813818(妻)</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>24</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="G44" s="6" t="inlineStr"/>
       <c r="H44" s="6" t="inlineStr"/>
       <c r="I44" s="6" t="inlineStr"/>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>屋主已換</t>
-        </is>
-      </c>
+      <c r="J44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1955,27 +1993,29 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>8B8</t>
+          <t>12A5</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>陳博凱</t>
+          <t>丁怡綾</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>0963-851782</t>
+          <t>0923-143930 / 0922-864279(夫)</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="G45" s="3" t="inlineStr"/>
+        <v>119</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>120</v>
+      </c>
       <c r="H45" s="3" t="inlineStr"/>
       <c r="I45" s="3" t="inlineStr"/>
       <c r="J45" s="4" t="inlineStr"/>
@@ -1987,25 +2027,25 @@
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>9B1</t>
+          <t>13A1</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>賴淑華</t>
+          <t>吳宗哲</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>0-</t>
+          <t>0958-622692(妻)</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>35</v>
+        <v>168</v>
       </c>
       <c r="G46" s="6" t="inlineStr"/>
       <c r="H46" s="6" t="inlineStr"/>
@@ -2019,27 +2059,29 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>9B2</t>
+          <t>13A2</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>洪于淵 / 蘇意雯</t>
+          <t>吳俊霖 / 賴品樺</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>0919-555917</t>
+          <t>0972-719012</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="G47" s="3" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>161</v>
+      </c>
       <c r="H47" s="3" t="inlineStr"/>
       <c r="I47" s="3" t="inlineStr"/>
       <c r="J47" s="4" t="inlineStr"/>
@@ -2051,25 +2093,25 @@
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>9B3</t>
+          <t>13A3</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>廖逸晴</t>
+          <t>俞紹輝</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>0985-606792 / 0910-372470(母)</t>
+          <t>0958-513119 / 0968-434634(妻)</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="G48" s="6" t="inlineStr"/>
       <c r="H48" s="6" t="inlineStr"/>
@@ -2083,29 +2125,27 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>9+10B5</t>
+          <t>13A5</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>陳麗雲</t>
+          <t>張志豪</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>0918-761366</t>
+          <t>0976-157506 / 0976-736173(妻)</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>21</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
       <c r="H49" s="3" t="inlineStr"/>
       <c r="I49" s="3" t="inlineStr"/>
       <c r="J49" s="4" t="inlineStr"/>
@@ -2117,27 +2157,29 @@
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>9+10B6</t>
+          <t>14A1</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>吳其蓉</t>
+          <t>廖英岑</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>0910-477148 / 0928-878816(夫)</t>
+          <t>0-</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>145</v>
-      </c>
-      <c r="G50" s="6" t="inlineStr"/>
+        <v>159</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>169</v>
+      </c>
       <c r="H50" s="6" t="inlineStr"/>
       <c r="I50" s="6" t="inlineStr"/>
       <c r="J50" s="7" t="inlineStr"/>
@@ -2149,27 +2191,29 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>9B7</t>
+          <t>14A2</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>高豐荏</t>
+          <t>張志安</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>0916-775106</t>
+          <t>0955-599225 / 0923-355226(妻)</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>140</v>
-      </c>
-      <c r="G51" s="3" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>53</v>
+      </c>
       <c r="H51" s="3" t="inlineStr"/>
       <c r="I51" s="3" t="inlineStr"/>
       <c r="J51" s="4" t="inlineStr"/>
@@ -2181,30 +2225,34 @@
         </is>
       </c>
       <c r="B52" s="6" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>9B8</t>
+          <t>14A3</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>詹益菖</t>
+          <t>吳琨翔</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>0-</t>
+          <t>0932-686996</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="G52" s="6" t="inlineStr"/>
       <c r="H52" s="6" t="inlineStr"/>
       <c r="I52" s="6" t="inlineStr"/>
-      <c r="J52" s="7" t="inlineStr"/>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>同 S1 屋主</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -2213,34 +2261,30 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>10B1</t>
+          <t>14A5</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>前：張筑瑀 / 新：何奕龍</t>
+          <t>陳玟沂</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>0933-403833</t>
+          <t>0988-330980 / 0926-241019(夫)</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="G53" s="3" t="inlineStr"/>
       <c r="H53" s="3" t="inlineStr"/>
       <c r="I53" s="3" t="inlineStr"/>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>屋主已換</t>
-        </is>
-      </c>
+      <c r="J53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -2249,32 +2293,36 @@
         </is>
       </c>
       <c r="B54" s="6" t="n">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>10B2</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>林敦品</t>
+          <t>黃國禎(租建材行) 租：余先生(承強)</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>0919-109979 / 1052-630736(夫)</t>
+          <t>0985-077777(余R) / 0900-615707(郭S)</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="H54" s="6" t="inlineStr"/>
       <c r="I54" s="6" t="inlineStr"/>
-      <c r="J54" s="7" t="inlineStr"/>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>建材行租戶</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -2283,30 +2331,34 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>10B3</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>謝薇欣</t>
+          <t>歐陽子元(租建材行)</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>0-</t>
+          <t>0985-077777(余R)</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="G55" s="3" t="inlineStr"/>
       <c r="H55" s="3" t="inlineStr"/>
       <c r="I55" s="3" t="inlineStr"/>
-      <c r="J55" s="4" t="inlineStr"/>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>建材行租戶</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -2315,25 +2367,25 @@
         </is>
       </c>
       <c r="B56" s="6" t="n">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>10B7</t>
+          <t>2B2</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>吳家慶</t>
+          <t>陳嘉彬</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>0988-896232 / 04-26225858</t>
+          <t>0-</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="G56" s="6" t="inlineStr"/>
       <c r="H56" s="6" t="inlineStr"/>
@@ -2347,32 +2399,30 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>104</v>
+        <v>55</v>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>10B8</t>
+          <t>2B3</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>王聿杰</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr"/>
+          <t>蔡亞臻</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>0931-474150 / 04-24738819</t>
+        </is>
+      </c>
       <c r="F57" s="5" t="n">
-        <v>83</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>96</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
       <c r="H57" s="3" t="inlineStr"/>
       <c r="I57" s="3" t="inlineStr"/>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>電話請補</t>
-        </is>
-      </c>
+      <c r="J57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -2381,32 +2431,32 @@
         </is>
       </c>
       <c r="B58" s="6" t="n">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>2B7</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>歐陽儷芳 / 租-蕭富仁</t>
+          <t>施碧虹</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>0982-611798 / 0970-992993(妻)</t>
+          <t>0- 同S6</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G58" s="6" t="inlineStr"/>
       <c r="H58" s="6" t="inlineStr"/>
       <c r="I58" s="6" t="inlineStr"/>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>出租中</t>
+          <t>電話同S6</t>
         </is>
       </c>
     </row>
@@ -2417,29 +2467,27 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>11B2</t>
+          <t>3B1</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>張志澤</t>
+          <t>甘慧之</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>0-</t>
+          <t>0988-861001</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>81</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>82</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
       <c r="H59" s="3" t="inlineStr"/>
       <c r="I59" s="3" t="inlineStr"/>
       <c r="J59" s="4" t="inlineStr"/>
@@ -2451,34 +2499,30 @@
         </is>
       </c>
       <c r="B60" s="6" t="n">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>11B3</t>
+          <t>3B2</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>施毓凡 / 租：王俊卿</t>
+          <t>楊政達</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>0912-627159 / 0917-517118(母)</t>
+          <t>0936-760105 / 0909-132606</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>150</v>
+        <v>39</v>
       </c>
       <c r="G60" s="6" t="inlineStr"/>
       <c r="H60" s="6" t="inlineStr"/>
       <c r="I60" s="6" t="inlineStr"/>
-      <c r="J60" s="7" t="inlineStr">
-        <is>
-          <t>出租中</t>
-        </is>
-      </c>
+      <c r="J60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -2487,25 +2531,25 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>11+12B5</t>
+          <t>3B3</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>黃子灝</t>
+          <t>郭慕慈</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>0931-632383</t>
+          <t>0-</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="G61" s="3" t="inlineStr"/>
       <c r="H61" s="3" t="inlineStr"/>
@@ -2519,25 +2563,25 @@
         </is>
       </c>
       <c r="B62" s="6" t="n">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>11+12B6</t>
+          <t>3+4B5</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>高明昊</t>
+          <t>邱若瑜</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>0966-077123 / 0953-117363(母)</t>
+          <t>0952-695232 / 0922-709299(夫)</t>
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>141</v>
+        <v>28</v>
       </c>
       <c r="G62" s="6" t="inlineStr"/>
       <c r="H62" s="6" t="inlineStr"/>
@@ -2551,25 +2595,25 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>11B7</t>
+          <t>3+4B6</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>李楓</t>
+          <t>黃姿綺</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>0988-963520</t>
+          <t>0912-758400</t>
         </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="G63" s="3" t="inlineStr"/>
       <c r="H63" s="3" t="inlineStr"/>
@@ -2583,36 +2627,30 @@
         </is>
       </c>
       <c r="B64" s="6" t="n">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>11B8</t>
+          <t>3B7</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>楊雅筑 / 租-賴罡成</t>
+          <t>周韋辰</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>0987-587164(夫) / 04-23368787</t>
+          <t>0987-797088 / 0937-252032</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>13</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="inlineStr"/>
       <c r="H64" s="6" t="inlineStr"/>
       <c r="I64" s="6" t="inlineStr"/>
-      <c r="J64" s="7" t="inlineStr">
-        <is>
-          <t>出租中</t>
-        </is>
-      </c>
+      <c r="J64" s="7" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -2621,34 +2659,30 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>12B1</t>
+          <t>3B8</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>原-白雅綺 / 現-盧靖鏵</t>
+          <t>盧宣名</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>0966-709908 / 盧：0960-666525</t>
+          <t>0-</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G65" s="3" t="inlineStr"/>
       <c r="H65" s="3" t="inlineStr"/>
       <c r="I65" s="3" t="inlineStr"/>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>屋主已換</t>
-        </is>
-      </c>
+      <c r="J65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -2657,25 +2691,25 @@
         </is>
       </c>
       <c r="B66" s="6" t="n">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>12B2</t>
+          <t>4B1</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>黃瑜瑜</t>
+          <t>黃軒奕</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>0918-024781 / 0922-757191(弟)</t>
+          <t>0936-709718 / 0985-441557(同住)</t>
         </is>
       </c>
       <c r="F66" s="5" t="n">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="G66" s="6" t="inlineStr"/>
       <c r="H66" s="6" t="inlineStr"/>
@@ -2689,34 +2723,30 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>12B3</t>
+          <t>4B2</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>監察委員-章秀琴</t>
+          <t>廖英如</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>0987-333483 / 0910-017537(夫)</t>
+          <t>0978-717518 / 04-24758092</t>
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="G67" s="3" t="inlineStr"/>
       <c r="H67" s="3" t="inlineStr"/>
       <c r="I67" s="3" t="inlineStr"/>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>監察委員</t>
-        </is>
-      </c>
+      <c r="J67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -2725,27 +2755,29 @@
         </is>
       </c>
       <c r="B68" s="6" t="n">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>12B7</t>
+          <t>4B3</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>童鈺婷</t>
+          <t>潘芳儀</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>0-</t>
+          <t>0975-781832 / 0970-520929(夫)</t>
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>135</v>
-      </c>
-      <c r="G68" s="6" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>34</v>
+      </c>
       <c r="H68" s="6" t="inlineStr"/>
       <c r="I68" s="6" t="inlineStr"/>
       <c r="J68" s="7" t="inlineStr"/>
@@ -2757,29 +2789,27 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>12B8</t>
+          <t>4B7</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>陳靜文</t>
+          <t>陳麗如</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>0919-068665 / 0926-065119(林R)</t>
+          <t>0-</t>
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>36</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
       <c r="H69" s="3" t="inlineStr"/>
       <c r="I69" s="3" t="inlineStr"/>
       <c r="J69" s="4" t="inlineStr"/>
@@ -2791,25 +2821,25 @@
         </is>
       </c>
       <c r="B70" s="6" t="n">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>13B1</t>
+          <t>4B8</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>王弘儒</t>
+          <t>黃美華</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>0952-932101 / 0931-515272(妻)</t>
+          <t>0975-043914 / 0935-602038</t>
         </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="G70" s="6" t="inlineStr"/>
       <c r="H70" s="6" t="inlineStr"/>
@@ -2823,34 +2853,30 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>13B2</t>
+          <t>5B1</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>江國全 / 租-李凱琳</t>
+          <t>張雅雯</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>0981-770793 / 0985-373169(同住)</t>
+          <t>0923-355242 / 0988-755886(夫)</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G71" s="3" t="inlineStr"/>
       <c r="H71" s="3" t="inlineStr"/>
       <c r="I71" s="3" t="inlineStr"/>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>出租中</t>
-        </is>
-      </c>
+      <c r="J71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -2859,25 +2885,25 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>13B3</t>
+          <t>5B2</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>江宏祥</t>
+          <t>朱明珍</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>0-</t>
+          <t>0953-928558</t>
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
       <c r="H72" s="6" t="inlineStr"/>
@@ -2891,25 +2917,25 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>13+14B5</t>
+          <t>5B3</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>何長億</t>
+          <t>張朝銘</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>0-</t>
+          <t>0953-775513 / 0921-498553</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>157</v>
+        <v>32</v>
       </c>
       <c r="G73" s="3" t="inlineStr"/>
       <c r="H73" s="3" t="inlineStr"/>
@@ -2923,34 +2949,30 @@
         </is>
       </c>
       <c r="B74" s="6" t="n">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>13+14B6</t>
+          <t>5+6B5</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>郭芳瑄</t>
+          <t>謝雨潤</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>0988-590374(屋主) / 0975-611092(母優先聯絡)</t>
+          <t>0980-152552 / 0928-261809(妻)</t>
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="G74" s="6" t="inlineStr"/>
       <c r="H74" s="6" t="inlineStr"/>
       <c r="I74" s="6" t="inlineStr"/>
-      <c r="J74" s="7" t="inlineStr">
-        <is>
-          <t>母優先聯絡</t>
-        </is>
-      </c>
+      <c r="J74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -2959,34 +2981,30 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>13B7</t>
+          <t>5+6B6</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>馮曉妏 / 租：外國人</t>
+          <t>林桂玉</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>0958-825383 / 0928-334375(夫)</t>
+          <t>0-</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="G75" s="3" t="inlineStr"/>
       <c r="H75" s="3" t="inlineStr"/>
       <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>出租中（外國人）</t>
-        </is>
-      </c>
+      <c r="J75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -2995,25 +3013,25 @@
         </is>
       </c>
       <c r="B76" s="6" t="n">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>13B8</t>
+          <t>5B7</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>高苹珊 古家諭</t>
+          <t>高袖華</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>0958-025332 / 0928-388559(父)</t>
+          <t>0986-635786 / 0937-285830(夫)</t>
         </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
       <c r="H76" s="6" t="inlineStr"/>
@@ -3027,29 +3045,27 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>14B1</t>
+          <t>5B8</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>楊鴻偉</t>
+          <t>賴雅惠</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>0-</t>
+          <t>0936-960900</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>143</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="G77" s="3" t="inlineStr"/>
       <c r="H77" s="3" t="inlineStr"/>
       <c r="I77" s="3" t="inlineStr"/>
       <c r="J77" s="4" t="inlineStr"/>
@@ -3061,16 +3077,16 @@
         </is>
       </c>
       <c r="B78" s="6" t="n">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>14+15B2</t>
+          <t>6B1</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>陳思恩</t>
+          <t>林桂鳳</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
@@ -3079,11 +3095,9 @@
         </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>131</v>
-      </c>
-      <c r="G78" s="5" t="n">
-        <v>132</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G78" s="6" t="inlineStr"/>
       <c r="H78" s="6" t="inlineStr"/>
       <c r="I78" s="6" t="inlineStr"/>
       <c r="J78" s="7" t="inlineStr"/>
@@ -3095,29 +3109,27 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>14+15B3</t>
+          <t>6B2</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>許慈玟</t>
+          <t>晉安</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>0-</t>
+          <t>0919-035076 / 0931-720858(同住) / 0912-750260</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G79" s="5" t="n">
-        <v>11</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="G79" s="3" t="inlineStr"/>
       <c r="H79" s="3" t="inlineStr"/>
       <c r="I79" s="3" t="inlineStr"/>
       <c r="J79" s="4" t="inlineStr"/>
@@ -3129,25 +3141,25 @@
         </is>
       </c>
       <c r="B80" s="6" t="n">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>14B7</t>
+          <t>6B3</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>徐家珍</t>
+          <t>張修毓</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>0987-748336 / 0939-885010(同住)</t>
+          <t>0921-628527(妻)</t>
         </is>
       </c>
       <c r="F80" s="5" t="n">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="G80" s="6" t="inlineStr"/>
       <c r="H80" s="6" t="inlineStr"/>
@@ -3161,29 +3173,27 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>14+15B8</t>
+          <t>6B7</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>詹欣翰</t>
+          <t>鄭永發</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>0-</t>
+          <t>0980-607784 / 0919-810888(妻)</t>
         </is>
       </c>
       <c r="F81" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>77</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="G81" s="3" t="inlineStr"/>
       <c r="H81" s="3" t="inlineStr"/>
       <c r="I81" s="3" t="inlineStr"/>
       <c r="J81" s="4" t="inlineStr"/>
@@ -3195,30 +3205,34 @@
         </is>
       </c>
       <c r="B82" s="6" t="n">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>15B1</t>
+          <t>6B8</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>王力慶</t>
+          <t>財務委員-洪冠華</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>0910-970899</t>
+          <t>0925-270614 / 0937-299595(父)</t>
         </is>
       </c>
       <c r="F82" s="5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G82" s="6" t="inlineStr"/>
       <c r="H82" s="6" t="inlineStr"/>
       <c r="I82" s="6" t="inlineStr"/>
-      <c r="J82" s="7" t="inlineStr"/>
+      <c r="J82" s="7" t="inlineStr">
+        <is>
+          <t>財務委員</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -3227,25 +3241,25 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>15B7</t>
+          <t>7B1</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>郭昌妮</t>
+          <t>張軒鴻</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>0-</t>
+          <t>0977-236156</t>
         </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="G83" s="3" t="inlineStr"/>
       <c r="H83" s="3" t="inlineStr"/>
@@ -3259,36 +3273,1668 @@
         </is>
       </c>
       <c r="B84" s="6" t="n">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>15B9</t>
+          <t>7B2</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>杜涵如</t>
+          <t>洪翊峰</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>0-</t>
+          <t>0919-745641 / 0932-677334(父)</t>
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>134</v>
+        <v>4</v>
       </c>
       <c r="G84" s="6" t="inlineStr"/>
       <c r="H84" s="6" t="inlineStr"/>
       <c r="I84" s="6" t="inlineStr"/>
-      <c r="J84" s="7">
+      <c r="J84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>7B3</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>吳弘信</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>0976-038366</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr"/>
+      <c r="G85" s="3" t="inlineStr"/>
+      <c r="H85" s="3" t="inlineStr"/>
+      <c r="I85" s="3" t="inlineStr"/>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>車位資料請複核</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>7+8B5</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>楊嘉凱</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>0989-748555(妻) / 0963-204310</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="G86" s="6" t="inlineStr"/>
+      <c r="H86" s="6" t="inlineStr"/>
+      <c r="I86" s="6" t="inlineStr"/>
+      <c r="J86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>7+8B6</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>詹偉哲</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>0932-247258(父)</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="G87" s="3" t="inlineStr"/>
+      <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr"/>
+      <c r="J87" s="4" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>7B7</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>吳振宇</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>0-</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="G88" s="6" t="inlineStr"/>
+      <c r="H88" s="6" t="inlineStr"/>
+      <c r="I88" s="6" t="inlineStr"/>
+      <c r="J88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>7B8</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>譚文政</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>0966-770876 / 0987-372895(妻)</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="G89" s="3" t="inlineStr"/>
+      <c r="H89" s="3" t="inlineStr"/>
+      <c r="I89" s="3" t="inlineStr"/>
+      <c r="J89" s="4" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>8B1</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>蘇欽洲</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>0919-631434 / 0937-781353(賴士超)</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="G90" s="6" t="inlineStr"/>
+      <c r="H90" s="6" t="inlineStr"/>
+      <c r="I90" s="6" t="inlineStr"/>
+      <c r="J90" s="7" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>8B2</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>曾昱泰</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>0988-173077</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="G91" s="3" t="inlineStr"/>
+      <c r="H91" s="3" t="inlineStr"/>
+      <c r="I91" s="3" t="inlineStr"/>
+      <c r="J91" s="4" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>8B3</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>黃礦衛</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>0934-072601 / 0930-671667(妻)</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="G92" s="6" t="inlineStr"/>
+      <c r="H92" s="6" t="inlineStr"/>
+      <c r="I92" s="6" t="inlineStr"/>
+      <c r="J92" s="7" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>8B7</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>前屋主：簡宗哲 / 新屋主：呂紹榮</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>0938-869298 / 0975-029305(妻)</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H93" s="3" t="inlineStr"/>
+      <c r="I93" s="3" t="inlineStr"/>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>屋主已換</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>8B8</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>陳博凱</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>0963-851782</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="G94" s="6" t="inlineStr"/>
+      <c r="H94" s="6" t="inlineStr"/>
+      <c r="I94" s="6" t="inlineStr"/>
+      <c r="J94" s="7" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>9B1</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>賴淑華</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>0-</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G95" s="3" t="inlineStr"/>
+      <c r="H95" s="3" t="inlineStr"/>
+      <c r="I95" s="3" t="inlineStr"/>
+      <c r="J95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>9B2</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>洪于淵 / 蘇意雯</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>0919-555917</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="G96" s="6" t="inlineStr"/>
+      <c r="H96" s="6" t="inlineStr"/>
+      <c r="I96" s="6" t="inlineStr"/>
+      <c r="J96" s="7" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>9B3</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>廖逸晴</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>0985-606792 / 0910-372470(母)</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="G97" s="3" t="inlineStr"/>
+      <c r="H97" s="3" t="inlineStr"/>
+      <c r="I97" s="3" t="inlineStr"/>
+      <c r="J97" s="4" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>9+10B5</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>陳麗雲</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>0918-761366</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H98" s="6" t="inlineStr"/>
+      <c r="I98" s="6" t="inlineStr"/>
+      <c r="J98" s="7" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>9+10B6</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>吳其蓉</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>0910-477148 / 0928-878816(夫)</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="G99" s="3" t="inlineStr"/>
+      <c r="H99" s="3" t="inlineStr"/>
+      <c r="I99" s="3" t="inlineStr"/>
+      <c r="J99" s="4" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>9B7</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>高豐荏</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>0916-775106</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="G100" s="6" t="inlineStr"/>
+      <c r="H100" s="6" t="inlineStr"/>
+      <c r="I100" s="6" t="inlineStr"/>
+      <c r="J100" s="7" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>9B8</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>詹益菖</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>0-</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G101" s="3" t="inlineStr"/>
+      <c r="H101" s="3" t="inlineStr"/>
+      <c r="I101" s="3" t="inlineStr"/>
+      <c r="J101" s="4" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>10B1</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>前：張筑瑀 / 新：何奕龍</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>0933-403833</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="G102" s="6" t="inlineStr"/>
+      <c r="H102" s="6" t="inlineStr"/>
+      <c r="I102" s="6" t="inlineStr"/>
+      <c r="J102" s="7" t="inlineStr">
+        <is>
+          <t>屋主已換</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>10B2</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>林敦品</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>0919-109979 / 1052-630736(夫)</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="H103" s="3" t="inlineStr"/>
+      <c r="I103" s="3" t="inlineStr"/>
+      <c r="J103" s="4" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>10B3</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>謝薇欣</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>0-</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="G104" s="6" t="inlineStr"/>
+      <c r="H104" s="6" t="inlineStr"/>
+      <c r="I104" s="6" t="inlineStr"/>
+      <c r="J104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>10B7</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>吳家慶</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>0988-896232 / 04-26225858</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="G105" s="3" t="inlineStr"/>
+      <c r="H105" s="3" t="inlineStr"/>
+      <c r="I105" s="3" t="inlineStr"/>
+      <c r="J105" s="4" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>10B8</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>王聿杰</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr"/>
+      <c r="F106" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="H106" s="6" t="inlineStr"/>
+      <c r="I106" s="6" t="inlineStr"/>
+      <c r="J106" s="7" t="inlineStr">
+        <is>
+          <t>電話請補</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>11B1</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>歐陽儷芳 / 租-蕭富仁</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>0982-611798 / 0970-992993(妻)</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="G107" s="3" t="inlineStr"/>
+      <c r="H107" s="3" t="inlineStr"/>
+      <c r="I107" s="3" t="inlineStr"/>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>出租中</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>11B2</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>張志澤</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>0-</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="H108" s="6" t="inlineStr"/>
+      <c r="I108" s="6" t="inlineStr"/>
+      <c r="J108" s="7" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>11B3</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>施毓凡 / 租：王俊卿</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>0912-627159 / 0917-517118(母)</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="G109" s="3" t="inlineStr"/>
+      <c r="H109" s="3" t="inlineStr"/>
+      <c r="I109" s="3" t="inlineStr"/>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>出租中</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>11+12B5</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>黃子灝</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>0931-632383</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>136</v>
+      </c>
+      <c r="G110" s="6" t="inlineStr"/>
+      <c r="H110" s="6" t="inlineStr"/>
+      <c r="I110" s="6" t="inlineStr"/>
+      <c r="J110" s="7" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>11+12B6</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>高明昊</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>0966-077123 / 0953-117363(母)</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="G111" s="3" t="inlineStr"/>
+      <c r="H111" s="3" t="inlineStr"/>
+      <c r="I111" s="3" t="inlineStr"/>
+      <c r="J111" s="4" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>11B7</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>李楓</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>0988-963520</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="G112" s="6" t="inlineStr"/>
+      <c r="H112" s="6" t="inlineStr"/>
+      <c r="I112" s="6" t="inlineStr"/>
+      <c r="J112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>11B8</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>楊雅筑 / 租-賴罡成</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>0987-587164(夫) / 04-23368787</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H113" s="3" t="inlineStr"/>
+      <c r="I113" s="3" t="inlineStr"/>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>出租中</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="n">
+        <v>112</v>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>12B1</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>原-白雅綺 / 現-盧靖鏵</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>0966-709908 / 盧：0960-666525</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G114" s="6" t="inlineStr"/>
+      <c r="H114" s="6" t="inlineStr"/>
+      <c r="I114" s="6" t="inlineStr"/>
+      <c r="J114" s="7" t="inlineStr">
+        <is>
+          <t>屋主已換</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>12B2</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>黃瑜瑜</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>0918-024781 / 0922-757191(弟)</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="G115" s="3" t="inlineStr"/>
+      <c r="H115" s="3" t="inlineStr"/>
+      <c r="I115" s="3" t="inlineStr"/>
+      <c r="J115" s="4" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="n">
+        <v>114</v>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>12B3</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>監察委員-章秀琴</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>0987-333483 / 0910-017537(夫)</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="G116" s="6" t="inlineStr"/>
+      <c r="H116" s="6" t="inlineStr"/>
+      <c r="I116" s="6" t="inlineStr"/>
+      <c r="J116" s="7" t="inlineStr">
+        <is>
+          <t>監察委員</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>12B7</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>童鈺婷</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>0-</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="G117" s="3" t="inlineStr"/>
+      <c r="H117" s="3" t="inlineStr"/>
+      <c r="I117" s="3" t="inlineStr"/>
+      <c r="J117" s="4" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="n">
+        <v>116</v>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>12B8</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>陳靜文</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>0919-068665 / 0926-065119(林R)</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="H118" s="6" t="inlineStr"/>
+      <c r="I118" s="6" t="inlineStr"/>
+      <c r="J118" s="7" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>13B1</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>王弘儒</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>0952-932101 / 0931-515272(妻)</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="G119" s="3" t="inlineStr"/>
+      <c r="H119" s="3" t="inlineStr"/>
+      <c r="I119" s="3" t="inlineStr"/>
+      <c r="J119" s="4" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="n">
+        <v>118</v>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>13B2</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>江國全 / 租-李凱琳</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>0981-770793 / 0985-373169(同住)</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="G120" s="6" t="inlineStr"/>
+      <c r="H120" s="6" t="inlineStr"/>
+      <c r="I120" s="6" t="inlineStr"/>
+      <c r="J120" s="7" t="inlineStr">
+        <is>
+          <t>出租中</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>13B3</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>江宏祥</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>0-</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="G121" s="3" t="inlineStr"/>
+      <c r="H121" s="3" t="inlineStr"/>
+      <c r="I121" s="3" t="inlineStr"/>
+      <c r="J121" s="4" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>13+14B5</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>何長億</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>0-</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="G122" s="6" t="inlineStr"/>
+      <c r="H122" s="6" t="inlineStr"/>
+      <c r="I122" s="6" t="inlineStr"/>
+      <c r="J122" s="7" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>13+14B6</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>郭芳瑄</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>0988-590374(屋主) / 0975-611092(母優先聯絡)</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="G123" s="3" t="inlineStr"/>
+      <c r="H123" s="3" t="inlineStr"/>
+      <c r="I123" s="3" t="inlineStr"/>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>母優先聯絡</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="n">
+        <v>122</v>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>13B7</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>馮曉妏 / 租：外國人</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>0958-825383 / 0928-334375(夫)</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="G124" s="6" t="inlineStr"/>
+      <c r="H124" s="6" t="inlineStr"/>
+      <c r="I124" s="6" t="inlineStr"/>
+      <c r="J124" s="7" t="inlineStr">
+        <is>
+          <t>出租中（外國人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>13B8</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>高苹珊 古家諭</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>0958-025332 / 0928-388559(父)</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G125" s="3" t="inlineStr"/>
+      <c r="H125" s="3" t="inlineStr"/>
+      <c r="I125" s="3" t="inlineStr"/>
+      <c r="J125" s="4" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>14B1</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>楊鴻偉</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>0-</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="H126" s="6" t="inlineStr"/>
+      <c r="I126" s="6" t="inlineStr"/>
+      <c r="J126" s="7" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>14+15B2</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>陳思恩</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>0-</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="H127" s="3" t="inlineStr"/>
+      <c r="I127" s="3" t="inlineStr"/>
+      <c r="J127" s="4" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>14+15B3</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>許慈玟</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>0-</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H128" s="6" t="inlineStr"/>
+      <c r="I128" s="6" t="inlineStr"/>
+      <c r="J128" s="7" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>14B7</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>徐家珍</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>0987-748336 / 0939-885010(同住)</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="G129" s="3" t="inlineStr"/>
+      <c r="H129" s="3" t="inlineStr"/>
+      <c r="I129" s="3" t="inlineStr"/>
+      <c r="J129" s="4" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>14+15B8</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>詹欣翰</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>0-</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="H130" s="6" t="inlineStr"/>
+      <c r="I130" s="6" t="inlineStr"/>
+      <c r="J130" s="7" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>15B1</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>王力慶</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>0910-970899</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G131" s="3" t="inlineStr"/>
+      <c r="H131" s="3" t="inlineStr"/>
+      <c r="I131" s="3" t="inlineStr"/>
+      <c r="J131" s="4" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>15B7</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>郭昌妮</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>0-</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="G132" s="6" t="inlineStr"/>
+      <c r="H132" s="6" t="inlineStr"/>
+      <c r="I132" s="6" t="inlineStr"/>
+      <c r="J132" s="7" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>時光嶼</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>15B9</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>杜涵如</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>0-</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="G133" s="3" t="inlineStr"/>
+      <c r="H133" s="3" t="inlineStr"/>
+      <c r="I133" s="3" t="inlineStr"/>
+      <c r="J133" s="4">
         <f> 15B6</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J84"/>
+  <autoFilter ref="A2:J133"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -3302,7 +4948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3477,6 +5123,30 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr"/>
+      <c r="B18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>合併備註</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>編號 1（S1）與編號 50（14A3）為同一屋主吳琨翔（同電話 0932-686996）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr"/>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>編號 51（14A5 陳玟沂）電話：0988-330980 / 0926-241019(夫)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
